--- a/assets/constructions/examples/ctd_mih_3075.xlsx
+++ b/assets/constructions/examples/ctd_mih_3075.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG6"/>
+  <dimension ref="A1:AK6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -594,11 +594,31 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M1200D100Z03M16HN07</t>
+          <t>M1200D025Z03M16HN07</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -612,10 +632,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>34.1</v>
+        <v>33.7</v>
       </c>
       <c r="E2" t="n">
-        <v>25.4</v>
+        <v>25</v>
       </c>
       <c r="F2" t="n">
         <v>17</v>
@@ -626,7 +646,7 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
-        <v>31.75</v>
+        <v>32</v>
       </c>
       <c r="K2" t="n">
         <v>3</v>
@@ -636,7 +656,7 @@
       </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
-        <v>19800</v>
+        <v>20000</v>
       </c>
       <c r="O2" t="n">
         <v>0.13</v>
@@ -698,14 +718,20 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>2019 /Novo</t>
-        </is>
-      </c>
+          <t>2017 / WIDIA основной каталог EN</t>
+        </is>
+      </c>
+      <c r="AH2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M1200D032Z03M16HN07</t>
+          <t>M1200D100Z03M16HN07</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -719,10 +745,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>40.7</v>
+        <v>34.1</v>
       </c>
       <c r="E3" t="n">
-        <v>32</v>
+        <v>25.4</v>
       </c>
       <c r="F3" t="n">
         <v>17</v>
@@ -733,7 +759,7 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
-        <v>40</v>
+        <v>31.75</v>
       </c>
       <c r="K3" t="n">
         <v>3</v>
@@ -743,10 +769,10 @@
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
-        <v>17600</v>
+        <v>19800</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2</v>
+        <v>0.13</v>
       </c>
       <c r="P3" t="n">
         <v>3.5</v>
@@ -805,14 +831,20 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>2017 / WIDIA основной каталог EN</t>
-        </is>
-      </c>
+          <t>2019 /Novo</t>
+        </is>
+      </c>
+      <c r="AH3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M1200D150Z04M16HN07</t>
+          <t>M1200D032Z04M16HN07</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -826,10 +858,10 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>46.8</v>
+        <v>40.7</v>
       </c>
       <c r="E4" t="n">
-        <v>38.1</v>
+        <v>32</v>
       </c>
       <c r="F4" t="n">
         <v>17</v>
@@ -840,7 +872,7 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
-        <v>38.1</v>
+        <v>40</v>
       </c>
       <c r="K4" t="n">
         <v>4</v>
@@ -850,10 +882,10 @@
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
-        <v>15800</v>
+        <v>17600</v>
       </c>
       <c r="O4" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="P4" t="n">
         <v>3.5</v>
@@ -907,19 +939,25 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>WID_M1200D_193</t>
+          <t>WID_M1200D_42</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>2019 /Novo</t>
-        </is>
-      </c>
+          <t>2017 / WIDIA основной каталог EN</t>
+        </is>
+      </c>
+      <c r="AH4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M1200D025Z03M16HN07</t>
+          <t>M1200D150Z04M16HN07</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -933,10 +971,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>33.7</v>
+        <v>46.8</v>
       </c>
       <c r="E5" t="n">
-        <v>25</v>
+        <v>38.1</v>
       </c>
       <c r="F5" t="n">
         <v>17</v>
@@ -947,20 +985,20 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
-        <v>32</v>
+        <v>38.1</v>
       </c>
       <c r="K5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
-        <v>20000</v>
+        <v>15800</v>
       </c>
       <c r="O5" t="n">
-        <v>0.13</v>
+        <v>0.22</v>
       </c>
       <c r="P5" t="n">
         <v>3.5</v>
@@ -1014,19 +1052,25 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>WID_M1200D_42</t>
+          <t>WID_M1200D_193</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>2017 / WIDIA основной каталог EN</t>
-        </is>
-      </c>
+          <t>2019 /Novo</t>
+        </is>
+      </c>
+      <c r="AH5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M1200D032Z04M16HN07</t>
+          <t>M1200D032Z03M16HN07</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1057,10 +1101,10 @@
         <v>40</v>
       </c>
       <c r="K6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
@@ -1129,6 +1173,12 @@
           <t>2017 / WIDIA основной каталог EN</t>
         </is>
       </c>
+      <c r="AH6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
